--- a/Tailieu/Soketoan2026/SochitietTK.xlsx
+++ b/Tailieu/Soketoan2026/SochitietTK.xlsx
@@ -7,6 +7,7 @@
   </x:bookViews>
   <x:sheets>
     <x:sheet name="111" sheetId="1" r:id="rId2"/>
+    <x:sheet name="112" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -19,10 +20,10 @@
     <x:t>Tên đơn vị</x:t>
   </x:si>
   <x:si>
-    <x:t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MST:3502550210</x:t>
+    <x:t>CÔNG TY TNHH THIẾT BỊ NỘI THẤT TRƯỜNG THỊNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MST:3502561068</x:t>
   </x:si>
   <x:si>
     <x:t>Mẫu số S03a-DNN</x:t>
@@ -37,7 +38,7 @@
     <x:t>(Dùng cho hình thức kế toán nhật ký chung)</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Từ tháng 5/2026 đến tháng 5/2026 </x:t>
+    <x:t xml:space="preserve">Từ tháng 6/2026 đến tháng 6/2026 </x:t>
   </x:si>
   <x:si>
     <x:t>111 - Tiền mặt</x:t>
@@ -73,7 +74,7 @@
     <x:t xml:space="preserve">Số dư đầu kỳ : </x:t>
   </x:si>
   <x:si>
-    <x:t>653.321.042</x:t>
+    <x:t>3.092.319.905</x:t>
   </x:si>
   <x:si>
     <x:t>Tổng phát sinh</x:t>
@@ -85,16 +86,16 @@
     <x:t>Phát sinh luỹ kế</x:t>
   </x:si>
   <x:si>
-    <x:t>26.232.612.570</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.150.471.834</x:t>
+    <x:t>191.471.988</x:t>
+  </x:si>
+  <x:si>
+    <x:t>776.543.293</x:t>
   </x:si>
   <x:si>
     <x:t>Số dư cuối kỳ</x:t>
   </x:si>
   <x:si>
-    <x:t>Ngày 31 tháng 5 năm 2026</x:t>
+    <x:t>Ngày 30 tháng 6 năm 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Người lập biểu</x:t>
@@ -107,6 +108,18 @@
   </x:si>
   <x:si>
     <x:t>(Ký, họ tên)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>112 - Tiền gửi ngân hàng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>344.545.911</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.376.969.140</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.065.719.725</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -908,4 +921,245 @@
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:H17"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="3" width="15.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25.710625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.710625" style="0" customWidth="1"/>
+    <x:col min="6" max="7" width="15.710625" style="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:8">
+      <x:c r="A1" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="3"/>
+      <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
+      <x:c r="F1" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G1" s="4"/>
+    </x:row>
+    <x:row r="2" spans="1:8">
+      <x:c r="A2" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B2" s="3"/>
+      <x:c r="C2" s="3"/>
+      <x:c r="D2" s="3"/>
+      <x:c r="F2" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G2" s="5"/>
+    </x:row>
+    <x:row r="3" spans="1:8">
+      <x:c r="F3" s="5"/>
+      <x:c r="G3" s="5"/>
+    </x:row>
+    <x:row r="4" spans="1:8">
+      <x:c r="A4" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="7"/>
+      <x:c r="G4" s="7"/>
+      <x:c r="H4" s="6"/>
+    </x:row>
+    <x:row r="5" spans="1:8">
+      <x:c r="A5" s="8" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B5" s="8"/>
+      <x:c r="C5" s="8"/>
+      <x:c r="D5" s="8"/>
+      <x:c r="E5" s="8"/>
+      <x:c r="F5" s="9"/>
+      <x:c r="G5" s="9"/>
+      <x:c r="H5" s="8"/>
+    </x:row>
+    <x:row r="6" spans="1:8">
+      <x:c r="A6" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B6" s="10"/>
+      <x:c r="C6" s="10"/>
+      <x:c r="D6" s="10"/>
+      <x:c r="E6" s="10"/>
+      <x:c r="F6" s="11"/>
+      <x:c r="G6" s="11"/>
+      <x:c r="H6" s="10"/>
+    </x:row>
+    <x:row r="7" spans="1:8">
+      <x:c r="A7" s="10" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B7" s="10"/>
+      <x:c r="C7" s="10"/>
+      <x:c r="D7" s="10"/>
+      <x:c r="E7" s="10"/>
+      <x:c r="F7" s="11"/>
+      <x:c r="G7" s="11"/>
+      <x:c r="H7" s="10"/>
+    </x:row>
+    <x:row r="8" spans="1:8">
+      <x:c r="A8" s="12" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B8" s="13" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C8" s="13"/>
+      <x:c r="D8" s="12" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E8" s="12" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G8" s="14"/>
+    </x:row>
+    <x:row r="9" spans="1:8">
+      <x:c r="A9" s="12"/>
+      <x:c r="B9" s="15" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D9" s="12"/>
+      <x:c r="E9" s="12"/>
+      <x:c r="F9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G9" s="16" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:8">
+      <x:c r="E10" s="17" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:8">
+      <x:c r="A11" s="19" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B11" s="19"/>
+      <x:c r="C11" s="19"/>
+      <x:c r="D11" s="19"/>
+      <x:c r="E11" s="19"/>
+      <x:c r="F11" s="19" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G11" s="19" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:8">
+      <x:c r="A12" s="19" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B12" s="19"/>
+      <x:c r="C12" s="19"/>
+      <x:c r="D12" s="19"/>
+      <x:c r="E12" s="19"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G12" s="19" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:8">
+      <x:c r="A13" s="19" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B13" s="19"/>
+      <x:c r="C13" s="19"/>
+      <x:c r="D13" s="19"/>
+      <x:c r="E13" s="19"/>
+      <x:c r="F13" s="19" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G13" s="19"/>
+    </x:row>
+    <x:row r="15" spans="1:8">
+      <x:c r="F15" s="20" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G15" s="20"/>
+    </x:row>
+    <x:row r="16" spans="1:8">
+      <x:c r="B16" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F16" s="21" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G16" s="21"/>
+    </x:row>
+    <x:row r="17" spans="1:8">
+      <x:c r="B17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F17" s="20" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G17" s="20"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells count="19">
+    <x:mergeCell ref="B1:E1"/>
+    <x:mergeCell ref="F1:G1"/>
+    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="F2:G3"/>
+    <x:mergeCell ref="A4:H4"/>
+    <x:mergeCell ref="A5:H5"/>
+    <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A7:H7"/>
+    <x:mergeCell ref="A8:A9"/>
+    <x:mergeCell ref="B8:C8"/>
+    <x:mergeCell ref="D8:D9"/>
+    <x:mergeCell ref="E8:E9"/>
+    <x:mergeCell ref="F8:G8"/>
+    <x:mergeCell ref="A11:E11"/>
+    <x:mergeCell ref="A12:E12"/>
+    <x:mergeCell ref="A13:E13"/>
+    <x:mergeCell ref="F15:G15"/>
+    <x:mergeCell ref="F16:G16"/>
+    <x:mergeCell ref="F17:G17"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>